--- a/Input_data/IST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -425,13 +425,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:F178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -446,20 +446,15 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>PREVIOUS</t>
+          <t>CONSENSUS</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>CONSENSUS</t>
+          <t>FORECAST</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>FORECAST</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>TIER</t>
         </is>
@@ -481,14 +476,9 @@
           <t>$6.81T</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>$6.81T</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="n">
+      <c r="F2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -500,31 +490,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -535,17 +520,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -553,12 +538,7 @@
           <t>0.3%</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
+      <c r="F4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -570,30 +550,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>-0.8%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
+      <c r="F5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -605,17 +580,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -623,12 +598,7 @@
           <t>0.3%</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
+      <c r="F6" t="n">
         <v>2</v>
       </c>
     </row>
@@ -640,31 +610,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>2</v>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -675,26 +636,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>3</v>
       </c>
     </row>
@@ -706,26 +662,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>3</v>
       </c>
     </row>
@@ -737,26 +688,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>3.7%</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -768,27 +714,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4.4%</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>3.7%</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>3</v>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -799,30 +744,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>3</v>
       </c>
     </row>
@@ -842,18 +778,13 @@
           <t>2%</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
         <is>
           <t>0.9%</t>
         </is>
       </c>
-      <c r="G13" t="n">
+      <c r="F13" t="n">
         <v>3</v>
       </c>
     </row>
@@ -865,26 +796,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>3</v>
       </c>
     </row>
@@ -896,31 +826,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>2</v>
+          <t>77.4%</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -931,31 +856,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>77.7%</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>77.4%</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>3</v>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -976,20 +896,15 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
           <t>-0.1%</t>
         </is>
       </c>
-      <c r="G17" t="n">
+      <c r="F17" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1011,7 +926,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1019,12 +934,7 @@
           <t>0.2%</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
+      <c r="F18" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1044,14 +954,9 @@
           <t>481</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="n">
+      <c r="F19" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1071,14 +976,9 @@
           <t>588</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>586</t>
-        </is>
-      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="n">
+      <c r="F20" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1096,1874 +996,3113 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="n">
+      <c r="F21" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-02-17 20:00:00+05:30</t>
+          <t>2025-02-15 01:30:00+05:30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fed Harker Speech</t>
+          <t>Fed Logan Speech</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="n">
+      <c r="F22" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-02-17 20:50:00+05:30</t>
+          <t>2025-02-17 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
+          <t>Fed Harker Speech</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="n">
+      <c r="F23" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-02-18 04:30:00+05:30</t>
+          <t>2025-02-17 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
+          <t>Fed Harker Speech</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="n">
+      <c r="F24" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-02-18 19:00:00+05:30</t>
+          <t>2025-02-17 20:50:00+05:30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexFEB</t>
+          <t>Fed Bowman Speech</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>-12.6</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-02-18 20:30:00+05:30</t>
+          <t>2025-02-17 20:50:00+05:30</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexFEB</t>
+          <t>Fed Bowman Speech</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-02-18 20:50:00+05:30</t>
+          <t>2025-02-18 04:30:00+05:30</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>Fed Waller Speech</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="n">
+      <c r="F27" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-02-18 22:00:00+05:30</t>
+          <t>2025-02-18 04:30:00+05:30</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>Fed Waller Speech</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>4.225%</t>
-        </is>
-      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="n">
-        <v>3</v>
+      <c r="F28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-02-18 22:00:00+05:30</t>
+          <t>2025-02-18 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>NY Empire State Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4.185%</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="n">
-        <v>3</v>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-02-18 22:30:00+05:30</t>
+          <t>2025-02-18 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NOPA Crush Report</t>
+          <t>NY Empire State Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="n">
-        <v>3</v>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-02-18 23:30:00+05:30</t>
+          <t>2025-02-18 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>NAHB Housing Market IndexFEB</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="n">
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-02-18 23:30:00+05:30</t>
+          <t>2025-02-18 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>NAHB Housing Market IndexFEB</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>4.025%</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="n">
-        <v>3</v>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-02-19 02:30:00+05:30</t>
+          <t>2025-02-18 20:50:00+05:30</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>$79B</t>
-        </is>
-      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="n">
+      <c r="F33" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-02-19 02:30:00+05:30</t>
+          <t>2025-02-18 20:50:00+05:30</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>$-15.8B</t>
-        </is>
-      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="n">
-        <v>3</v>
+      <c r="F34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-02-19 02:30:00+05:30</t>
+          <t>2025-02-18 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>$159.9B</t>
-        </is>
-      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="n">
+      <c r="F35" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-02-19 17:30:00+05:30</t>
+          <t>2025-02-18 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>153.1</t>
-        </is>
-      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="n">
+      <c r="F36" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-02-19 17:30:00+05:30</t>
+          <t>2025-02-18 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>640.6</t>
-        </is>
-      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="n">
+      <c r="F37" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-02-19 17:30:00+05:30</t>
+          <t>2025-02-18 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>230.0</t>
-        </is>
-      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="n">
+      <c r="F38" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-02-19 17:30:00+05:30</t>
+          <t>2025-02-18 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>NOPA Crush Report</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="n">
+      <c r="F39" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-02-19 17:30:00+05:30</t>
+          <t>2025-02-18 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>NOPA Crush Report</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>6.95%</t>
-        </is>
-      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="n">
-        <v>2</v>
+      <c r="F40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-02-19 19:00:00+05:30</t>
+          <t>2025-02-18 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>1.482M</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>1.47M</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>1</v>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-02-19 19:00:00+05:30</t>
+          <t>2025-02-18 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>1.499M</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>1.35M</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>1</v>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-02-19 19:00:00+05:30</t>
+          <t>2025-02-18 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>-0.8%</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
+      <c r="F43" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-02-19 19:00:00+05:30</t>
+          <t>2025-02-18 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>15.8%</t>
-        </is>
-      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>-9.0%</t>
-        </is>
-      </c>
-      <c r="G44" t="n">
-        <v>2</v>
+      <c r="F44" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025-02-19 19:25:00+05:30</t>
+          <t>2025-02-19 02:30:00+05:30</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Redbook YoYFEB/15</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>5.3%</t>
-        </is>
-      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="n">
+      <c r="F45" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025-02-19 21:00:00+05:30</t>
+          <t>2025-02-19 02:30:00+05:30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 22.5 to 30 yrs</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>$50 million</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="n">
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025-02-19 22:00:00+05:30</t>
+          <t>2025-02-19 02:30:00+05:30</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>4.230%</t>
-        </is>
-      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="n">
-        <v>3</v>
+      <c r="F47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025-02-19 23:30:00+05:30</t>
+          <t>2025-02-19 02:30:00+05:30</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20-Year Bond Auction</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>4.900%</t>
-        </is>
-      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="n">
+      <c r="F48" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025-02-20 00:30:00+05:30</t>
+          <t>2025-02-19 02:30:00+05:30</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FOMC Minutes</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="n">
-        <v>1</v>
+      <c r="F49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2025-02-20 03:00:00+05:30</t>
+          <t>2025-02-19 02:30:00+05:30</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>API Crude Oil Stock ChangeFEB/14</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>9.043M</t>
-        </is>
-      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="n">
+      <c r="F50" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2025-02-20 03:30:00+05:30</t>
+          <t>2025-02-19 17:30:00+05:30</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Fed Jefferson Speech</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="n">
-        <v>2</v>
+      <c r="F51" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2025-02-20 19:00:00+05:30</t>
+          <t>2025-02-19 17:30:00+05:30</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>42.9</t>
-        </is>
-      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="n">
+      <c r="F52" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2025-02-20 19:00:00+05:30</t>
+          <t>2025-02-19 17:30:00+05:30</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>31.9</t>
-        </is>
-      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="n">
+      <c r="F53" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2025-02-20 19:00:00+05:30</t>
+          <t>2025-02-19 17:30:00+05:30</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>11.9</t>
-        </is>
-      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="n">
-        <v>3</v>
+      <c r="F54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2025-02-20 19:00:00+05:30</t>
+          <t>2025-02-19 17:30:00+05:30</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>46.3</t>
-        </is>
-      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="n">
-        <v>3</v>
+      <c r="F55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2025-02-20 19:00:00+05:30</t>
+          <t>2025-02-19 17:30:00+05:30</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="n">
+      <c r="F56" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2025-02-20 19:00:00+05:30</t>
+          <t>2025-02-19 17:30:00+05:30</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>1850K</t>
-        </is>
-      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
-      <c r="G57" t="n">
+      <c r="F57" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2025-02-20 19:00:00+05:30</t>
+          <t>2025-02-19 17:30:00+05:30</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="G58" t="n">
-        <v>2</v>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2025-02-20 19:00:00+05:30</t>
+          <t>2025-02-19 17:30:00+05:30</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
-      <c r="G59" t="n">
-        <v>2</v>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2025-02-20 19:00:00+05:30</t>
+          <t>2025-02-19 17:30:00+05:30</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
-      <c r="G60" t="n">
+      <c r="F60" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2025-02-20 20:05:00+05:30</t>
+          <t>2025-02-19 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Fed Golsbee Speech</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="n">
-        <v>2</v>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1.45M</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>1.47M</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2025-02-20 20:30:00+05:30</t>
+          <t>2025-02-19 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CB Leading Index MoMJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>1.39M</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G62" t="n">
-        <v>3</v>
+          <t>1.35M</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2025-02-20 21:00:00+05:30</t>
+          <t>2025-02-19 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>EIA Natural Gas Stocks ChangeFEB/14</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>-100Bcf</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="n">
-        <v>3</v>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>-0.8%</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2025-02-20 22:00:00+05:30</t>
+          <t>2025-02-19 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>4.250%</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="n">
-        <v>3</v>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>-9.0%</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2025-02-20 22:00:00+05:30</t>
+          <t>2025-02-19 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>4.240%</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="n">
-        <v>3</v>
+          <t>1.45M</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>1.47M</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2025-02-20 22:30:00+05:30</t>
+          <t>2025-02-19 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>0.135M</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="n">
-        <v>3</v>
+          <t>1.39M</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>1.35M</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025-02-20 22:30:00+05:30</t>
+          <t>2025-02-19 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>0.082M</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="n">
-        <v>3</v>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>-0.8%</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025-02-20 22:30:00+05:30</t>
+          <t>2025-02-19 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>-0.009M</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="n">
-        <v>3</v>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>-9.0%</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2025-02-20 22:30:00+05:30</t>
+          <t>2025-02-19 19:25:00+05:30</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>Redbook YoYFEB/15</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>0.159M</t>
-        </is>
-      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="n">
+      <c r="F69" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025-02-20 22:30:00+05:30</t>
+          <t>2025-02-19 19:25:00+05:30</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>Redbook YoYFEB/15</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>0.872M</t>
-        </is>
-      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="n">
+      <c r="F70" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025-02-20 22:30:00+05:30</t>
+          <t>2025-02-19 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>NY Fed Treasury Purchases 22.5 to 30 yrs</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>$50 million</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="n">
+      <c r="F71" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025-02-20 22:30:00+05:30</t>
+          <t>2025-02-19 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>NY Fed Treasury Purchases 22.5 to 30 yrs</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>6.87%</t>
+          <t>$50 million</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="n">
+      <c r="F72" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025-02-20 22:30:00+05:30</t>
+          <t>2025-02-19 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>6.09%</t>
-        </is>
-      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="n">
+      <c r="F73" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-02-20 22:30:00+05:30</t>
+          <t>2025-02-19 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>-3.035M</t>
-        </is>
-      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="n">
-        <v>2</v>
+      <c r="F74" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-02-20 22:30:00+05:30</t>
+          <t>2025-02-19 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>20-Year Bond Auction</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>-0.184M</t>
-        </is>
-      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="n">
+      <c r="F75" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025-02-20 22:30:00+05:30</t>
+          <t>2025-02-19 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>20-Year Bond Auction</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>4.07M</t>
-        </is>
-      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="n">
-        <v>2</v>
+      <c r="F76" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2025-02-20 22:35:00+05:30</t>
+          <t>2025-02-20 00:30:00+05:30</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>FOMC Minutes</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="n">
-        <v>2</v>
+      <c r="F77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2025-02-20 23:30:00+05:30</t>
+          <t>2025-02-20 00:30:00+05:30</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>30-Year TIPS Auction</t>
+          <t>FOMC Minutes</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>2.055%</t>
-        </is>
-      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="n">
-        <v>3</v>
+      <c r="F78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2025-02-21 01:00:00+05:30</t>
+          <t>2025-02-20 03:00:00+05:30</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>API Crude Oil Stock ChangeFEB/14</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="n">
+      <c r="F79" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025-02-21 03:00:00+05:30</t>
+          <t>2025-02-20 03:00:00+05:30</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Fed Balance SheetFEB/19</t>
+          <t>API Crude Oil Stock ChangeFEB/14</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>$6.81T</t>
-        </is>
-      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="n">
-        <v>3</v>
+      <c r="F80" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025-02-21 03:30:00+05:30</t>
+          <t>2025-02-20 03:30:00+05:30</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>Fed Jefferson Speech</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="n">
+      <c r="F81" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025-02-21 20:15:00+05:30</t>
+          <t>2025-02-20 03:30:00+05:30</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>Fed Jefferson Speech</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>51.2</t>
-        </is>
-      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="G82" t="n">
+      <c r="F82" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025-02-21 20:15:00+05:30</t>
+          <t>2025-02-20 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>52.9</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>52.7</t>
-        </is>
-      </c>
-      <c r="G83" t="n">
-        <v>2</v>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025-02-21 20:15:00+05:30</t>
+          <t>2025-02-20 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>52.7</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>52.7</t>
-        </is>
-      </c>
-      <c r="G84" t="n">
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2025-02-21 20:30:00+05:30</t>
+          <t>2025-02-20 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="G85" t="n">
+          <t>1879.0K</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025-02-21 20:30:00+05:30</t>
+          <t>2025-02-20 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>4.17M</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>4.16M</t>
-        </is>
-      </c>
-      <c r="G86" t="n">
-        <v>1</v>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025-02-21 20:30:00+05:30</t>
+          <t>2025-02-20 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>-1.7%</t>
-        </is>
-      </c>
-      <c r="G87" t="n">
-        <v>2</v>
+      <c r="F87" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025-02-21 20:30:00+05:30</t>
+          <t>2025-02-20 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>71.1</t>
-        </is>
-      </c>
+      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="G88" t="n">
-        <v>2</v>
+          <t>219.0K</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2025-02-21 20:30:00+05:30</t>
+          <t>2025-02-20 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="G89" t="n">
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2025-02-21 20:30:00+05:30</t>
+          <t>2025-02-20 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>69.3</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>67.3</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>67.3</t>
-        </is>
-      </c>
-      <c r="G90" t="n">
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2025-02-21 20:30:00+05:30</t>
+          <t>2025-02-20 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>68.7</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>68.7</t>
-        </is>
-      </c>
-      <c r="G91" t="n">
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2025-02-21 22:00:00+05:30</t>
+          <t>2025-02-20 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Fed Jefferson Speech</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="n">
-        <v>2</v>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2025-02-21 23:30:00+05:30</t>
+          <t>2025-02-20 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
+      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="n">
+      <c r="F93" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2025-02-21 23:30:00+05:30</t>
+          <t>2025-02-20 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>481</t>
-        </is>
-      </c>
+      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="n">
+      <c r="F94" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2025-02-24 19:00:00+05:30</t>
+          <t>2025-02-20 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Chicago Fed National Activity IndexJAN</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="n">
+          <t>216K</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2025-02-24 21:00:00+05:30</t>
+          <t>2025-02-20 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Dallas Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>14.1</t>
-        </is>
-      </c>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="n">
-        <v>2</v>
+      <c r="F96" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2025-02-24 22:00:00+05:30</t>
+          <t>2025-02-20 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="n">
+      <c r="F97" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2025-02-24 22:00:00+05:30</t>
+          <t>2025-02-20 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="n">
+      <c r="F98" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2025-02-24 23:30:00+05:30</t>
+          <t>2025-02-20 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2-Year Note Auction</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="n">
+      <c r="F99" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2025-02-20 19:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Initial Jobless ClaimsFEB/15</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2025-02-20 20:05:00+05:30</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Fed Golsbee Speech</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2025-02-20 20:05:00+05:30</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Fed Golsbee Speech</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2025-02-20 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>CB Leading Index MoMJAN</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2025-02-20 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>CB Leading Index MoMJAN</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2025-02-20 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>EIA Natural Gas Stocks ChangeFEB/14</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2025-02-20 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>EIA Natural Gas Stocks ChangeFEB/14</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2025-02-20 22:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>8-Week Bill Auction</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2025-02-20 22:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>4-Week Bill Auction</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2025-02-20 22:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>8-Week Bill Auction</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2025-02-20 22:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>4-Week Bill Auction</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2025-02-20 22:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2025-02-20 22:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2025-02-20 22:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2025-02-20 22:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2025-02-20 22:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>15-Year Mortgage RateFEB/20</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2025-02-20 22:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>30-Year Mortgage RateFEB/20</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2025-02-20 22:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2025-02-20 22:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2025-02-20 22:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2025-02-20 22:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2025-02-20 22:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2025-02-20 22:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>15-Year Mortgage RateFEB/20</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2025-02-20 22:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>30-Year Mortgage RateFEB/20</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2025-02-20 22:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2025-02-20 22:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2025-02-20 22:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2025-02-20 22:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2025-02-20 22:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2025-02-20 22:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2025-02-20 22:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2025-02-20 22:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2025-02-20 22:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2025-02-20 22:35:00+05:30</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Fed Musalem Speech</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2025-02-20 22:35:00+05:30</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Fed Musalem Speech</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2025-02-20 23:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>30-Year TIPS Auction</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2025-02-20 23:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>30-Year TIPS Auction</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2025-02-21 01:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Fed Barr Speech</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2025-02-21 01:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Fed Barr Speech</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2025-02-21 03:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Fed Balance SheetFEB/19</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2025-02-21 03:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Fed Balance SheetFEB/19</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2025-02-21 03:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Fed Kugler Speech</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2025-02-21 03:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Fed Kugler Speech</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2025-02-21 20:15:00+05:30</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>52.7</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2025-02-21 20:15:00+05:30</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>51.3</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2025-02-21 20:15:00+05:30</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>52.7</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2025-02-21 20:15:00+05:30</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>51.3</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2025-02-21 20:15:00+05:30</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>52.7</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2025-02-21 20:15:00+05:30</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>52.7</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2025-02-21 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Michigan Inflation Expectations FinalFEB</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2025-02-21 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Michigan Current Conditions FinalFEB</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>68.7</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>68.7</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2025-02-21 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Michigan Consumer Expectations FinalFEB</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2025-02-21 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2025-02-21 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>67.8</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>67.8</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2025-02-21 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Existing Home SalesJAN</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>4.17M</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>4.16M</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2025-02-21 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Existing Home Sales MoMJAN</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>-1.7%</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2025-02-21 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Michigan Consumer Expectations FinalFEB</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2025-02-21 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Michigan Inflation Expectations FinalFEB</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2025-02-21 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Existing Home SalesJAN</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>4.17M</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>4.16M</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2025-02-21 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Existing Home Sales MoMJAN</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>-1.7%</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2025-02-21 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>67.8</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>67.8</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2025-02-21 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Michigan Current Conditions FinalFEB</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>68.7</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>68.7</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2025-02-21 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2025-02-21 22:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Fed Jefferson Speech</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2025-02-21 22:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Fed Jefferson Speech</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2025-02-21 23:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2025-02-21 23:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2025-02-21 23:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2025-02-21 23:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2025-02-24 19:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Chicago Fed National Activity IndexJAN</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2025-02-24 19:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Chicago Fed National Activity IndexJAN</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2025-02-24 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Dallas Fed Manufacturing IndexFEB</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2025-02-24 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Dallas Fed Manufacturing IndexFEB</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2025-02-24 22:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>6-Month Bill Auction</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2025-02-24 22:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>3-Month Bill Auction</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2025-02-24 22:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>6-Month Bill Auction</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2025-02-24 22:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>3-Month Bill Auction</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr"/>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2025-02-24 23:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2-Year Note Auction</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr"/>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2025-02-24 23:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2-Year Note Auction</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr"/>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="n">
         <v>3</v>
       </c>
     </row>

--- a/Input_data/IST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -744,18 +744,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>77.8%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -770,18 +774,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -796,26 +804,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -826,22 +834,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>77.8%</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>77.7%</t>
-        </is>
-      </c>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -856,26 +860,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -1472,14 +1472,14 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -1526,14 +1526,14 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -1562,14 +1562,14 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -1598,14 +1598,14 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -1634,14 +1634,14 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1724,14 +1724,14 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -1816,18 +1816,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1.45M</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -1838,22 +1842,18 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -1864,22 +1864,18 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -1890,18 +1886,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -2194,18 +2194,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -2216,7 +2220,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -2252,22 +2256,14 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
@@ -2278,12 +2274,16 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F87" t="n">
         <v>3</v>
       </c>
@@ -2296,18 +2296,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
@@ -2318,7 +2322,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -2336,14 +2340,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
@@ -2354,7 +2366,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -2372,22 +2384,18 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
@@ -2398,14 +2406,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -2416,14 +2432,14 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -2438,22 +2454,18 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
@@ -2464,7 +2476,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -2482,22 +2494,14 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
@@ -2508,16 +2512,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="n">
         <v>3</v>
       </c>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -2780,14 +2780,14 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -2816,14 +2816,14 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -2888,14 +2888,14 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -3122,14 +3122,14 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -3360,14 +3360,14 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F144" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -3448,14 +3448,14 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -3470,22 +3470,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
@@ -3496,18 +3496,18 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -3548,18 +3548,18 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -3574,22 +3574,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="154">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="155">
@@ -3626,18 +3626,22 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="156">
@@ -3648,22 +3652,18 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>68.7</t>
-        </is>
-      </c>
+      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157">
@@ -3674,22 +3674,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158">
@@ -3752,18 +3752,22 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>68.7</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161">
@@ -3800,18 +3804,14 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
+      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F162" t="n">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -4042,7 +4042,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>

--- a/Input_data/IST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -744,18 +744,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>77.8%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -770,26 +774,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -800,18 +800,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -826,22 +830,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>77.8%</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>77.7%</t>
-        </is>
-      </c>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -856,26 +856,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -1864,22 +1864,18 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -1890,18 +1886,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -2960,14 +2960,14 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123">
@@ -2978,14 +2978,14 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -3032,14 +3032,14 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127">
@@ -3050,14 +3050,14 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128">
@@ -3360,14 +3360,14 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F144" t="n">
@@ -3448,14 +3448,14 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -3496,22 +3496,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="151">
@@ -3648,18 +3648,18 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -3752,22 +3752,22 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>

--- a/Input_data/IST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -744,22 +744,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>77.8%</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>77.7%</t>
-        </is>
-      </c>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -774,18 +770,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -800,26 +800,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -830,18 +830,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>77.8%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -856,26 +860,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1864,18 +1864,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -1886,22 +1890,18 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -2960,14 +2960,14 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123">
@@ -2978,14 +2978,14 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -3032,14 +3032,14 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="127">
@@ -3050,14 +3050,14 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128">
@@ -3360,14 +3360,14 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F144" t="n">
@@ -3448,14 +3448,14 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -3496,18 +3496,18 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -3648,22 +3648,22 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157">
@@ -3752,22 +3752,22 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>

--- a/Input_data/IST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F178"/>
+  <dimension ref="A1:F184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,26 +490,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -520,26 +520,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -550,26 +546,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.8%</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -580,26 +572,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -610,18 +598,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -636,22 +624,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>-0.8%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -662,22 +654,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -688,22 +684,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>1.3%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -714,26 +714,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -946,12 +946,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/14</t>
+          <t>Baker Hughes Total Rigs CountFEB/14</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>588</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -968,12 +968,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/14</t>
+          <t>Baker Hughes Oil Rig CountFEB/14</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>481</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -1454,14 +1454,14 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -1472,14 +1472,14 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -1490,14 +1490,14 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -1544,14 +1544,14 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -1598,14 +1598,14 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -1688,14 +1688,14 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -1742,22 +1742,18 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -1768,22 +1764,18 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -1794,14 +1786,14 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -1816,18 +1808,18 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>1.45M</t>
+          <t>1.39M</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -1842,18 +1834,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1.45M</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -1886,18 +1882,18 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1.39M</t>
+          <t>1.45M</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -1912,18 +1908,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -2194,22 +2194,18 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
@@ -2220,22 +2216,18 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -2272,18 +2264,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -2294,16 +2290,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="n">
         <v>3</v>
       </c>
@@ -2316,7 +2308,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -2334,14 +2326,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
@@ -2352,14 +2352,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
@@ -2370,12 +2378,16 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F91" t="n">
         <v>3</v>
       </c>
@@ -2388,12 +2400,16 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F92" t="n">
         <v>3</v>
       </c>
@@ -2406,22 +2422,14 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
@@ -2432,16 +2440,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="n">
         <v>3</v>
       </c>
@@ -2454,16 +2458,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="n">
         <v>3</v>
       </c>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -2780,14 +2780,14 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -2798,14 +2798,14 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -2888,14 +2888,14 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119">
@@ -2906,14 +2906,14 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -2960,14 +2960,14 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123">
@@ -2978,14 +2978,14 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -3032,14 +3032,14 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="127">
@@ -3050,14 +3050,14 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -3338,14 +3338,14 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F143" t="n">
@@ -3382,14 +3382,14 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F145" t="n">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F146" t="n">
@@ -3448,14 +3448,14 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -3470,22 +3470,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="150">
@@ -3496,22 +3496,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="151">
@@ -3548,18 +3548,18 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -3574,22 +3574,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154">
@@ -3622,22 +3622,22 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -3648,22 +3648,18 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>68.7</t>
-        </is>
-      </c>
+      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157">
@@ -3674,22 +3670,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158">
@@ -3700,22 +3696,22 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159">
@@ -3726,22 +3722,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160">
@@ -3752,22 +3748,22 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
@@ -3778,18 +3774,18 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F161" t="n">
@@ -3804,18 +3800,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>68.7</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -4106,6 +4106,118 @@
         <v>3</v>
       </c>
     </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2025-02-25 19:25:00+05:30</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Redbook YoYFEB/22</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr"/>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2025-02-25 19:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>House Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2025-02-25 19:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr"/>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2025-02-25 19:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>House Price IndexDEC</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2025-02-25 19:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>House Price Index MoMDEC</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2025-02-25 19:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Input_data/IST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F184"/>
+  <dimension ref="A1:F194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -886,26 +886,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Business Inventories MoMDEC</t>
+          <t>Retail Inventories Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -916,26 +916,26 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMDEC</t>
+          <t>Business Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>-0.1%</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -1598,14 +1598,14 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -1670,14 +1670,14 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -1688,14 +1688,14 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1724,14 +1724,14 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -1764,18 +1764,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -1786,18 +1790,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1.45M</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -1834,22 +1842,18 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -1860,14 +1864,14 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -1908,22 +1912,18 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -2194,16 +2194,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
         <v>3</v>
       </c>
@@ -2216,18 +2212,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -2238,18 +2238,18 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -2264,18 +2264,18 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -2290,12 +2290,16 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F87" t="n">
         <v>3</v>
       </c>
@@ -2308,12 +2312,16 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F88" t="n">
         <v>3</v>
       </c>
@@ -2326,22 +2334,14 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
@@ -2352,22 +2352,14 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
@@ -2378,16 +2370,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="n">
         <v>3</v>
       </c>
@@ -2400,16 +2388,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="n">
         <v>3</v>
       </c>
@@ -2422,14 +2406,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -2440,7 +2432,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -2458,7 +2450,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -2494,7 +2486,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -2512,7 +2504,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -2530,12 +2522,16 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F99" t="n">
         <v>3</v>
       </c>
@@ -2548,12 +2544,16 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F100" t="n">
         <v>3</v>
       </c>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -2762,14 +2762,14 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -2888,14 +2888,14 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -2960,14 +2960,14 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123">
@@ -2978,14 +2978,14 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -3050,14 +3050,14 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -3140,14 +3140,14 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -3382,14 +3382,14 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F145" t="n">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F146" t="n">
@@ -3470,18 +3470,18 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -3496,22 +3496,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151">
@@ -3522,22 +3522,18 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>67.3</t>
-        </is>
-      </c>
+      <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152">
@@ -3548,22 +3544,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -3574,22 +3570,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="154">
@@ -3600,18 +3596,22 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>68.7</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="155">
@@ -3622,22 +3622,18 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>4.17M</t>
-        </is>
-      </c>
+      <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="156">
@@ -3648,18 +3644,22 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="157">
@@ -3670,22 +3670,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158">
@@ -3696,22 +3696,22 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159">
@@ -3722,22 +3722,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160">
@@ -3748,22 +3748,22 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161">
@@ -3774,18 +3774,18 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F161" t="n">
@@ -3800,18 +3800,18 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F162" t="n">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -4127,12 +4127,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2025-02-25 19:30:00+05:30</t>
+          <t>2025-02-25 19:25:00+05:30</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>Redbook YoYFEB/22</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
@@ -4150,18 +4150,14 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E181" t="inlineStr"/>
       <c r="F181" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="182">
@@ -4172,7 +4168,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -4190,7 +4186,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -4218,6 +4214,194 @@
         <v>3</v>
       </c>
     </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2025-02-25 19:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr"/>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2025-02-25 19:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2025-02-25 19:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2025-02-25 19:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>House Price Index MoMDEC</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2025-02-25 19:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>House Price IndexDEC</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2025-02-25 19:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>House Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2025-02-25 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2025-02-25 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>CB Consumer ConfidenceFEB</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr"/>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2025-02-25 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr"/>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2025-02-25 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr"/>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Input_data/IST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F194"/>
+  <dimension ref="A1:F200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,26 +490,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -520,22 +520,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -546,22 +550,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>-0.8%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -572,18 +580,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -598,22 +606,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>1.3%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -624,26 +636,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.8%</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -654,26 +662,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -684,26 +688,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -714,26 +718,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -946,12 +946,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/14</t>
+          <t>Baker Hughes Oil Rig CountFEB/14</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>481</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -968,12 +968,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/14</t>
+          <t>Baker Hughes Total Rigs CountFEB/14</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>588</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -1382,14 +1382,14 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -1400,14 +1400,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -1418,14 +1418,14 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -1436,14 +1436,14 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -1490,14 +1490,14 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -1544,14 +1544,14 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -1616,14 +1616,14 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -1688,14 +1688,14 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1742,18 +1742,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -1764,18 +1768,18 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1.39M</t>
+          <t>1.45M</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -1790,22 +1794,18 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -1816,22 +1816,18 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -1842,18 +1838,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1.45M</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -1886,18 +1886,18 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1.45M</t>
+          <t>1.39M</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -2212,22 +2212,18 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -2238,22 +2234,18 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
@@ -2264,22 +2256,14 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
@@ -2290,16 +2274,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="n">
         <v>3</v>
       </c>
@@ -2312,16 +2292,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="n">
         <v>3</v>
       </c>
@@ -2334,7 +2310,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -2352,14 +2328,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
@@ -2370,12 +2354,16 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F91" t="n">
         <v>3</v>
       </c>
@@ -2388,12 +2376,16 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F92" t="n">
         <v>3</v>
       </c>
@@ -2406,22 +2398,14 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
@@ -2432,7 +2416,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -2450,7 +2434,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -2468,7 +2452,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -2486,14 +2470,22 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F97" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
@@ -2504,14 +2496,22 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F98" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
@@ -2522,16 +2522,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="n">
         <v>3</v>
       </c>
@@ -2544,18 +2540,22 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
@@ -2762,14 +2762,14 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -2780,14 +2780,14 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -2906,14 +2906,14 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -2942,14 +2942,14 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -3122,14 +3122,14 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
@@ -3140,14 +3140,14 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
@@ -3338,14 +3338,14 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F143" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -3382,14 +3382,14 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F145" t="n">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F146" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -3448,14 +3448,14 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -3470,18 +3470,18 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -3496,18 +3496,14 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
+      <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -3522,18 +3518,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="152">
@@ -3544,22 +3544,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="153">
@@ -3570,18 +3570,18 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -3596,18 +3596,18 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -3622,18 +3622,22 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>4.17M</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -3644,18 +3648,18 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -3670,22 +3674,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158">
@@ -3696,22 +3700,18 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>67.3</t>
-        </is>
-      </c>
+      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159">
@@ -3722,22 +3722,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
@@ -3774,18 +3774,18 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F161" t="n">
@@ -3800,18 +3800,18 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F162" t="n">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -4150,14 +4150,18 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="182">
@@ -4168,7 +4172,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -4186,7 +4190,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -4204,7 +4208,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -4222,18 +4226,14 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E185" t="inlineStr"/>
       <c r="F185" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -4244,18 +4244,14 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187">
@@ -4266,7 +4262,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
@@ -4302,7 +4298,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
@@ -4320,14 +4316,18 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr"/>
-      <c r="E190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F190" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="191">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
@@ -4392,13 +4392,121 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2025-02-25 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2025-02-25 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr"/>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2025-02-25 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr"/>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2025-02-25 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr"/>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2025-02-25 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Dallas Fed Services IndexFEB</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2025-02-25 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr"/>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="n">
         <v>3</v>
       </c>
     </row>

--- a/Input_data/IST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F202"/>
+  <dimension ref="A1:F204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -744,26 +744,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -774,18 +774,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -800,18 +800,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>77.8%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -826,22 +830,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -856,26 +860,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -1418,14 +1418,14 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -1436,14 +1436,14 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -1616,14 +1616,14 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -1652,14 +1652,14 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1838,14 +1838,14 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -1860,18 +1860,18 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>1.39M</t>
+          <t>1.45M</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -1886,22 +1886,18 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -1912,18 +1908,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -2194,22 +2194,14 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
@@ -2272,22 +2264,18 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
@@ -2298,7 +2286,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -2316,7 +2304,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -2334,7 +2322,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -2352,7 +2340,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -2370,18 +2358,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -2392,18 +2384,22 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -2548,12 +2544,16 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F100" t="n">
         <v>3</v>
       </c>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -2906,14 +2906,14 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -3032,14 +3032,14 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="127">
@@ -3050,14 +3050,14 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128">
@@ -3068,14 +3068,14 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -3360,14 +3360,14 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F144" t="n">
@@ -3448,14 +3448,14 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -3648,22 +3648,18 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>67.3</t>
-        </is>
-      </c>
+      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157">
@@ -3674,18 +3670,18 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F157" t="n">
@@ -3700,22 +3696,22 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159">
@@ -3752,22 +3748,22 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161">
@@ -3804,18 +3800,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -4042,7 +4042,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -4204,18 +4204,14 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E184" t="inlineStr"/>
       <c r="F184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -4226,7 +4222,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -4244,14 +4240,18 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F186" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="187">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -4410,14 +4410,14 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="196">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -4464,14 +4464,14 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="199">
@@ -4546,6 +4546,42 @@
         <v>3</v>
       </c>
     </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2025-02-25 23:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>5-Year Note Auction</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr"/>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2025-02-25 23:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Money SupplyJAN</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
